--- a/reports/selected-rooms.xlsx
+++ b/reports/selected-rooms.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1939,9 +1939,23 @@
         <v>2026-10-07T09:24:25.921Z</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>completes the room booking and sandbox payment</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Chapter London Bridge, London</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Diamond Ensuite Shared West Facing</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-10-07T10:03:48.910Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D110"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D111"/>
   </ignoredErrors>
 </worksheet>
 </file>